--- a/02_DIA_inicio_2026_analisis_assets/rbd_9416_escuela-poetas-de-chile_nt1_nucleos.xlsx
+++ b/02_DIA_inicio_2026_analisis_assets/rbd_9416_escuela-poetas-de-chile_nt1_nucleos.xlsx
@@ -775,13 +775,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FFB9D465-3C4E-4AB2-B65B-665AF9B6AA57}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3A68CB73-02AE-4174-8AB8-51D6408DDC31}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8C1D4658-6007-4461-93B0-F2012CB71390}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EB2D919F-4F6F-4A4A-BA14-1D0BD4558153}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FA961437-A5B6-46B4-80C8-948031F8F8F5}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3A5D45CD-8C97-4288-8BF5-DBBAD8197AA0}"/>
 </file>